--- a/laboratorios/Sesion02/laboratorioI_medicion_pib.xlsx
+++ b/laboratorios/Sesion02/laboratorioI_medicion_pib.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulogarridogrijalva/Documents/Docencia/2026/III/Macroeconomía/macroeconomia-200fp/laboratorios/sesion02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4A5708-A82D-3047-B63B-13ED52684096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C1611F-8E7C-F04C-99C1-1E529E754680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inicio" sheetId="1" r:id="rId1"/>
@@ -329,10 +329,9 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Celda de entrada: complete con información del Banco de Guatemala o con el dato solicitado.</t>
         </r>
@@ -811,10 +810,9 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Supuesto académico del caso ANDAR GT, S.A. Puede modificarse para análisis de sensibilidad.</t>
         </r>
@@ -905,10 +903,9 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Incluya: tamaño del mercado nacional, mercado objetivo, pares demandados en los tres escenarios, coherencia de la capacidad y recomendación de avanzar o no.</t>
         </r>
@@ -1302,7 +1299,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="\Q\ #,##0.00"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1420,6 +1417,12 @@
       <sz val="11"/>
       <color rgb="FFF97316"/>
       <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1606,57 +1609,51 @@
     <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1664,8 +1661,14 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1711,6 +1714,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="es-GT"/>
               <a:t>Consumo final privado de calzado, 2013–2024</a:t>
             </a:r>
           </a:p>
@@ -1852,6 +1856,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="es-GT"/>
                   <a:t>Año</a:t>
                 </a:r>
               </a:p>
@@ -1888,6 +1893,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="es-GT"/>
                   <a:t>Millones de quetzales</a:t>
                 </a:r>
               </a:p>
@@ -1933,6 +1939,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="es-GT"/>
               <a:t>Pares demandados vs. capacidad máxima</a:t>
             </a:r>
           </a:p>
@@ -2051,15 +2058,6 @@
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>30000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>30000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>30000</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2098,6 +2096,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="es-GT"/>
                   <a:t>Escenario</a:t>
                 </a:r>
               </a:p>
@@ -2134,6 +2133,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="es-GT"/>
                   <a:t>Pares</a:t>
                 </a:r>
               </a:p>
@@ -2537,7 +2537,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16"/>
@@ -2549,7 +2549,7 @@
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="16"/>
@@ -2561,7 +2561,7 @@
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="26"/>
+      <c r="A3" s="20"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -2571,7 +2571,7 @@
       <c r="H3" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="31" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="16"/>
@@ -2589,7 +2589,7 @@
       <c r="G6" s="16"/>
     </row>
     <row r="8" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="17" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="16"/>
@@ -2602,28 +2602,28 @@
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="26"/>
       <c r="D9" s="16"/>
       <c r="E9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="15"/>
+      <c r="F9" s="26"/>
       <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="26"/>
       <c r="D10" s="16"/>
       <c r="E10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="15"/>
+      <c r="F10" s="26"/>
       <c r="G10" s="16"/>
     </row>
     <row r="12" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="16"/>
@@ -2633,7 +2633,7 @@
       <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="27" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="16"/>
@@ -2643,7 +2643,7 @@
       <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="16"/>
@@ -2653,7 +2653,7 @@
       <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="16"/>
@@ -2663,7 +2663,7 @@
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="27" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="16"/>
@@ -2673,7 +2673,7 @@
       <c r="G16" s="16"/>
     </row>
     <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="27" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="16"/>
@@ -2683,7 +2683,7 @@
       <c r="G17" s="16"/>
     </row>
     <row r="19" spans="2:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="17" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="16"/>
@@ -2697,7 +2697,7 @@
         <v>15</v>
       </c>
       <c r="C20" s="16"/>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="24" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="16"/>
@@ -2705,11 +2705,11 @@
       <c r="G20" s="16"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="30" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="16"/>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="24" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="16"/>
@@ -2717,11 +2717,11 @@
       <c r="G21" s="16"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="29" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="16"/>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="24" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="16"/>
@@ -2733,7 +2733,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="16"/>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="24" t="s">
         <v>22</v>
       </c>
       <c r="E23" s="16"/>
@@ -2741,7 +2741,7 @@
       <c r="G23" s="16"/>
     </row>
     <row r="25" spans="2:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="17" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="16"/>
@@ -2751,7 +2751,7 @@
       <c r="G25" s="16"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="23" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="16"/>
@@ -2770,6 +2770,18 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B5:G6"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B8:G8"/>
     <mergeCell ref="B26:G27"/>
     <mergeCell ref="D20:G20"/>
     <mergeCell ref="B23:C23"/>
@@ -2784,18 +2796,6 @@
     <mergeCell ref="B12:G12"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B13:G13"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B5:G6"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B8:G8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2825,7 +2825,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="18" t="s">
         <v>25</v>
       </c>
       <c r="B1" s="16"/>
@@ -2837,7 +2837,7 @@
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="21" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="16"/>
@@ -2849,7 +2849,7 @@
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="26"/>
+      <c r="A3" s="20"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -2859,7 +2859,7 @@
       <c r="H3" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="22" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="16"/>
@@ -2969,7 +2969,7 @@
       <c r="F15" s="3"/>
     </row>
     <row r="18" spans="1:6" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="17" t="s">
         <v>42</v>
       </c>
       <c r="B18" s="16"/>
@@ -3013,7 +3013,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="19" t="s">
         <v>47</v>
       </c>
       <c r="B24" s="16"/>
@@ -3023,7 +3023,7 @@
       <c r="F24" s="16"/>
     </row>
     <row r="25" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="30"/>
+      <c r="A25" s="15"/>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
@@ -3055,7 +3055,7 @@
       <c r="F28" s="16"/>
     </row>
     <row r="30" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="19" t="s">
         <v>48</v>
       </c>
       <c r="B30" s="16"/>
@@ -3065,7 +3065,7 @@
       <c r="F30" s="16"/>
     </row>
     <row r="31" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="30"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
       <c r="D31" s="16"/>
@@ -3144,7 +3144,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="18" t="s">
         <v>49</v>
       </c>
       <c r="B1" s="16"/>
@@ -3157,7 +3157,7 @@
       <c r="I1" s="16"/>
     </row>
     <row r="2" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="21" t="s">
         <v>50</v>
       </c>
       <c r="B2" s="16"/>
@@ -3170,7 +3170,7 @@
       <c r="I2" s="16"/>
     </row>
     <row r="3" spans="1:9" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="26"/>
+      <c r="A3" s="20"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -3323,7 +3323,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="17" t="s">
         <v>54</v>
       </c>
       <c r="B22" s="16"/>
@@ -3333,10 +3333,7 @@
       <c r="A23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="7" t="e">
-        <f>IF(OR(B14="",B15=""),"",B15/B14-1)</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="B23" s="7"/>
     </row>
     <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -3351,22 +3348,16 @@
       <c r="A25" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="7" t="e">
-        <f>IF(OR(B18="",B19=""),"",B19/B18-1)</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="B25" s="7"/>
     </row>
     <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="7" t="e">
-        <f>IF(OR(B8="",B19=""),"",(B19/B8)^(1/11)-1)</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="B26" s="7"/>
     </row>
     <row r="29" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="19" t="s">
         <v>59</v>
       </c>
       <c r="B29" s="16"/>
@@ -3378,7 +3369,7 @@
       <c r="H29" s="16"/>
     </row>
     <row r="30" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="30"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
@@ -3428,7 +3419,7 @@
       <c r="H34" s="16"/>
     </row>
     <row r="36" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="19" t="s">
         <v>60</v>
       </c>
       <c r="B36" s="16"/>
@@ -3440,7 +3431,7 @@
       <c r="H36" s="16"/>
     </row>
     <row r="37" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="30"/>
+      <c r="A37" s="15"/>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
@@ -3491,6 +3482,7 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A37:H41"/>
     <mergeCell ref="A3:I3"/>
@@ -3498,7 +3490,6 @@
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.55000000000000004" bottom="0.55000000000000004" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
@@ -3530,7 +3521,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="18" t="s">
         <v>61</v>
       </c>
       <c r="B1" s="16"/>
@@ -3542,7 +3533,7 @@
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="21" t="s">
         <v>62</v>
       </c>
       <c r="B2" s="16"/>
@@ -3554,7 +3545,7 @@
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="26"/>
+      <c r="A3" s="20"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -3564,7 +3555,7 @@
       <c r="H3" s="16"/>
     </row>
     <row r="6" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="17" t="s">
         <v>63</v>
       </c>
       <c r="B6" s="16"/>
@@ -3582,7 +3573,7 @@
         <v>65</v>
       </c>
       <c r="D7" s="16"/>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="33" t="s">
         <v>66</v>
       </c>
       <c r="G7" s="16"/>
@@ -3612,7 +3603,7 @@
         <v>65</v>
       </c>
       <c r="D9" s="16"/>
-      <c r="F9" s="34">
+      <c r="F9" s="35">
         <f>B17</f>
         <v>0</v>
       </c>
@@ -3641,7 +3632,7 @@
         <v>65</v>
       </c>
       <c r="D11" s="16"/>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="37" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="16"/>
@@ -3671,20 +3662,20 @@
         <v>65</v>
       </c>
       <c r="D13" s="16"/>
-      <c r="F13" s="34">
+      <c r="F13" s="35">
         <f>B18</f>
         <v>0</v>
       </c>
       <c r="G13" s="16"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="34" t="s">
         <v>74</v>
       </c>
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="17" t="s">
         <v>75</v>
       </c>
       <c r="B16" s="16"/>
@@ -3697,15 +3688,12 @@
       <c r="A17" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="4">
-        <f>Etapa1_Datos!F12</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="37" t="s">
+      <c r="B17" s="4"/>
+      <c r="C17" s="36" t="s">
         <v>77</v>
       </c>
       <c r="D17" s="16"/>
-      <c r="F17" s="34">
+      <c r="F17" s="35">
         <f>B19</f>
         <v>0</v>
       </c>
@@ -3715,11 +3703,8 @@
       <c r="A18" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="4">
-        <f>B17*B7</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="37" t="s">
+      <c r="B18" s="4"/>
+      <c r="C18" s="36" t="s">
         <v>79</v>
       </c>
       <c r="D18" s="16"/>
@@ -3728,17 +3713,14 @@
       <c r="A19" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="4">
-        <f>B18*B8</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="37" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="36" t="s">
         <v>81</v>
       </c>
       <c r="D19" s="16"/>
     </row>
     <row r="23" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="19" t="s">
         <v>82</v>
       </c>
       <c r="B23" s="16"/>
@@ -3749,7 +3731,7 @@
       <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="30"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
@@ -3803,7 +3785,7 @@
       <c r="G29" s="16"/>
     </row>
     <row r="31" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="19" t="s">
         <v>83</v>
       </c>
       <c r="B31" s="16"/>
@@ -3814,7 +3796,7 @@
       <c r="G31" s="16"/>
     </row>
     <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="30"/>
+      <c r="A32" s="15"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
@@ -3851,6 +3833,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A32:G35"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="A2:H2"/>
@@ -3867,15 +3858,6 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A24:G29"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.55000000000000004" bottom="0.55000000000000004" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
@@ -3906,7 +3888,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="18" t="s">
         <v>84</v>
       </c>
       <c r="B1" s="16"/>
@@ -3918,7 +3900,7 @@
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="21" t="s">
         <v>85</v>
       </c>
       <c r="B2" s="16"/>
@@ -3930,7 +3912,7 @@
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="26"/>
+      <c r="A3" s="20"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -3961,14 +3943,8 @@
         <f>Etapa3_Mercado!B10</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C8" s="4">
-        <f>Etapa3_Mercado!B19*B8</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="12">
-        <f>IF(C8="","",C8*1000000/Etapa3_Mercado!B9)</f>
-        <v>0</v>
-      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="12"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -3978,14 +3954,8 @@
         <f>Etapa3_Mercado!B11</f>
         <v>0.02</v>
       </c>
-      <c r="C9" s="4">
-        <f>Etapa3_Mercado!B19*B9</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="12">
-        <f>IF(C9="","",C9*1000000/Etapa3_Mercado!B9)</f>
-        <v>0</v>
-      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
@@ -3995,17 +3965,11 @@
         <f>Etapa3_Mercado!B12</f>
         <v>0.03</v>
       </c>
-      <c r="C10" s="4">
-        <f>Etapa3_Mercado!B19*B10</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="12">
-        <f>IF(C10="","",C10*1000000/Etapa3_Mercado!B9)</f>
-        <v>0</v>
-      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="12"/>
     </row>
     <row r="13" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="17" t="s">
         <v>93</v>
       </c>
       <c r="B13" s="16"/>
@@ -4031,7 +3995,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="19" t="s">
         <v>96</v>
       </c>
       <c r="B18" s="16"/>
@@ -4042,7 +4006,7 @@
       <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="30"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
@@ -4096,7 +4060,7 @@
       <c r="G24" s="16"/>
     </row>
     <row r="26" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="19" t="s">
         <v>97</v>
       </c>
       <c r="B26" s="16"/>
@@ -4107,7 +4071,7 @@
       <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="30"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -4179,7 +4143,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="18" t="s">
         <v>98</v>
       </c>
       <c r="B1" s="16"/>
@@ -4191,7 +4155,7 @@
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="21" t="s">
         <v>99</v>
       </c>
       <c r="B2" s="16"/>
@@ -4203,7 +4167,7 @@
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="26"/>
+      <c r="A3" s="20"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -4240,22 +4204,10 @@
         <f>Etapa4_Demanda!D8</f>
         <v>0</v>
       </c>
-      <c r="C8" s="12">
-        <f>Etapa3_Mercado!B13</f>
-        <v>30000</v>
-      </c>
-      <c r="D8" s="12">
-        <f>MIN(B8,C8)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="11">
-        <f>IF(C8=0,"",D8/C8)</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="13">
-        <f>D8*Etapa3_Mercado!B9</f>
-        <v>0</v>
-      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="13"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -4265,22 +4217,10 @@
         <f>Etapa4_Demanda!D9</f>
         <v>0</v>
       </c>
-      <c r="C9" s="12">
-        <f>Etapa3_Mercado!B13</f>
-        <v>30000</v>
-      </c>
-      <c r="D9" s="12">
-        <f>MIN(B9,C9)</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="11">
-        <f>IF(C9=0,"",D9/C9)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="13">
-        <f>D9*Etapa3_Mercado!B9</f>
-        <v>0</v>
-      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="13"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
@@ -4290,25 +4230,13 @@
         <f>Etapa4_Demanda!D10</f>
         <v>0</v>
       </c>
-      <c r="C10" s="12">
-        <f>Etapa3_Mercado!B13</f>
-        <v>30000</v>
-      </c>
-      <c r="D10" s="12">
-        <f>MIN(B10,C10)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="11">
-        <f>IF(C10=0,"",D10/C10)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="13">
-        <f>D10*Etapa3_Mercado!B9</f>
-        <v>0</v>
-      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="13"/>
     </row>
     <row r="31" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="19" t="s">
         <v>104</v>
       </c>
       <c r="B31" s="16"/>
@@ -4318,7 +4246,7 @@
       <c r="F31" s="16"/>
     </row>
     <row r="32" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="30"/>
+      <c r="A32" s="15"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
@@ -4366,7 +4294,7 @@
       <c r="F37" s="16"/>
     </row>
     <row r="39" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29" t="s">
+      <c r="A39" s="19" t="s">
         <v>105</v>
       </c>
       <c r="B39" s="16"/>
@@ -4376,7 +4304,7 @@
       <c r="F39" s="16"/>
     </row>
     <row r="40" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="30"/>
+      <c r="A40" s="15"/>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
@@ -4409,13 +4337,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A40:F43"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A32:F37"/>
-    <mergeCell ref="A40:F43"/>
-    <mergeCell ref="A31:F31"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.55000000000000004" bottom="0.55000000000000004" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
@@ -4442,7 +4370,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="18" t="s">
         <v>106</v>
       </c>
       <c r="B1" s="16"/>
@@ -4454,7 +4382,7 @@
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="21" t="s">
         <v>107</v>
       </c>
       <c r="B2" s="16"/>
@@ -4466,7 +4394,7 @@
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="26"/>
+      <c r="A3" s="20"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -4476,7 +4404,7 @@
       <c r="H3" s="16"/>
     </row>
     <row r="6" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="17" t="s">
         <v>108</v>
       </c>
       <c r="B6" s="16"/>
@@ -4554,7 +4482,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="17" t="s">
         <v>114</v>
       </c>
       <c r="B15" s="16"/>
@@ -4696,7 +4624,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="17" t="s">
         <v>116</v>
       </c>
       <c r="B31" s="16"/>
@@ -4708,7 +4636,7 @@
       <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="19" t="s">
         <v>117</v>
       </c>
       <c r="B32" s="16"/>
@@ -4720,7 +4648,7 @@
       <c r="H32" s="16"/>
     </row>
     <row r="33" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="30"/>
+      <c r="A33" s="15"/>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
       <c r="D33" s="16"/>
@@ -4750,7 +4678,7 @@
       <c r="H35" s="16"/>
     </row>
     <row r="37" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="19" t="s">
         <v>118</v>
       </c>
       <c r="B37" s="16"/>
@@ -4762,7 +4690,7 @@
       <c r="H37" s="16"/>
     </row>
     <row r="38" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="30"/>
+      <c r="A38" s="15"/>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
@@ -4792,7 +4720,7 @@
       <c r="H40" s="16"/>
     </row>
     <row r="42" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="29" t="s">
+      <c r="A42" s="19" t="s">
         <v>119</v>
       </c>
       <c r="B42" s="16"/>
@@ -4804,7 +4732,7 @@
       <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="30"/>
+      <c r="A43" s="15"/>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
@@ -4834,7 +4762,7 @@
       <c r="H45" s="16"/>
     </row>
     <row r="47" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="29" t="s">
+      <c r="A47" s="19" t="s">
         <v>120</v>
       </c>
       <c r="B47" s="16"/>
@@ -4846,7 +4774,7 @@
       <c r="H47" s="16"/>
     </row>
     <row r="48" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="30"/>
+      <c r="A48" s="15"/>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
       <c r="D48" s="16"/>
@@ -4876,7 +4804,7 @@
       <c r="H50" s="16"/>
     </row>
     <row r="53" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="19" t="s">
+      <c r="A53" s="17" t="s">
         <v>121</v>
       </c>
       <c r="B53" s="16"/>
@@ -4921,6 +4849,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A43:H45"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A7:C7"/>
     <mergeCell ref="A48:H50"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A54:H56"/>
@@ -4937,14 +4873,6 @@
     <mergeCell ref="A33:H35"/>
     <mergeCell ref="A38:H40"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A43:H45"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.55000000000000004" bottom="0.55000000000000004" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="portrait"/>

--- a/laboratorios/Sesion02/laboratorioI_medicion_pib.xlsx
+++ b/laboratorios/Sesion02/laboratorioI_medicion_pib.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulogarridogrijalva/Documents/Docencia/2026/III/Macroeconomía/macroeconomia-200fp/laboratorios/sesion02/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulogarridogrijalva/Documents/Docencia/2026/III/Macroeconomía/macroeconomia-200fp/laboratorios/Sesion02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C1611F-8E7C-F04C-99C1-1E529E754680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168EC748-2EEF-B845-88DF-F78FB5B07017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1619,26 +1619,41 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1646,14 +1661,15 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1661,25 +1677,9 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2571,7 +2571,7 @@
       <c r="H3" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="16"/>
@@ -2602,24 +2602,24 @@
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="26"/>
+      <c r="C9" s="28"/>
       <c r="D9" s="16"/>
       <c r="E9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="26"/>
+      <c r="F9" s="28"/>
       <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="26"/>
+      <c r="C10" s="28"/>
       <c r="D10" s="16"/>
       <c r="E10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="28"/>
       <c r="G10" s="16"/>
     </row>
     <row r="12" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -2633,7 +2633,7 @@
       <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="29" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="16"/>
@@ -2643,7 +2643,7 @@
       <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="29" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="16"/>
@@ -2653,7 +2653,7 @@
       <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="29" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="16"/>
@@ -2663,7 +2663,7 @@
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="29" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="16"/>
@@ -2673,7 +2673,7 @@
       <c r="G16" s="16"/>
     </row>
     <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="29" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="16"/>
@@ -2693,11 +2693,11 @@
       <c r="G19" s="16"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="16"/>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="26" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="16"/>
@@ -2705,11 +2705,11 @@
       <c r="G20" s="16"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="27" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="16"/>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="26" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="16"/>
@@ -2717,11 +2717,11 @@
       <c r="G21" s="16"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="34" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="16"/>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="26" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="16"/>
@@ -2729,11 +2729,11 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="32" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="16"/>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="26" t="s">
         <v>22</v>
       </c>
       <c r="E23" s="16"/>
@@ -2751,7 +2751,7 @@
       <c r="G25" s="16"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="31" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="16"/>
@@ -2770,18 +2770,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B5:G6"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B8:G8"/>
     <mergeCell ref="B26:G27"/>
     <mergeCell ref="D20:G20"/>
     <mergeCell ref="B23:C23"/>
@@ -2796,6 +2784,18 @@
     <mergeCell ref="B12:G12"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B13:G13"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B5:G6"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B8:G8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2859,7 +2859,7 @@
       <c r="H3" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="35" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="16"/>
@@ -3013,7 +3013,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="23" t="s">
         <v>47</v>
       </c>
       <c r="B24" s="16"/>
@@ -3055,7 +3055,7 @@
       <c r="F28" s="16"/>
     </row>
     <row r="30" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="23" t="s">
         <v>48</v>
       </c>
       <c r="B30" s="16"/>
@@ -3357,7 +3357,7 @@
       <c r="B26" s="7"/>
     </row>
     <row r="29" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="23" t="s">
         <v>59</v>
       </c>
       <c r="B29" s="16"/>
@@ -3419,7 +3419,7 @@
       <c r="H34" s="16"/>
     </row>
     <row r="36" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="19" t="s">
+      <c r="A36" s="23" t="s">
         <v>60</v>
       </c>
       <c r="B36" s="16"/>
@@ -3569,11 +3569,11 @@
       <c r="B7" s="8">
         <v>0.3</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="36" t="s">
         <v>65</v>
       </c>
       <c r="D7" s="16"/>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="39" t="s">
         <v>66</v>
       </c>
       <c r="G7" s="16"/>
@@ -3585,7 +3585,7 @@
       <c r="B8" s="8">
         <v>0.25</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="36" t="s">
         <v>65</v>
       </c>
       <c r="D8" s="16"/>
@@ -3599,11 +3599,11 @@
       <c r="B9" s="9">
         <v>420</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="36" t="s">
         <v>65</v>
       </c>
       <c r="D9" s="16"/>
-      <c r="F9" s="35">
+      <c r="F9" s="38">
         <f>B17</f>
         <v>0</v>
       </c>
@@ -3616,7 +3616,7 @@
       <c r="B10" s="8">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="36" t="s">
         <v>65</v>
       </c>
       <c r="D10" s="16"/>
@@ -3628,7 +3628,7 @@
       <c r="B11" s="8">
         <v>0.02</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="36" t="s">
         <v>65</v>
       </c>
       <c r="D11" s="16"/>
@@ -3644,7 +3644,7 @@
       <c r="B12" s="8">
         <v>0.03</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="36" t="s">
         <v>65</v>
       </c>
       <c r="D12" s="16"/>
@@ -3658,18 +3658,18 @@
       <c r="B13" s="10">
         <v>30000</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="36" t="s">
         <v>65</v>
       </c>
       <c r="D13" s="16"/>
-      <c r="F13" s="35">
+      <c r="F13" s="38">
         <f>B18</f>
         <v>0</v>
       </c>
       <c r="G13" s="16"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F15" s="34" t="s">
+      <c r="F15" s="40" t="s">
         <v>74</v>
       </c>
       <c r="G15" s="16"/>
@@ -3689,11 +3689,11 @@
         <v>76</v>
       </c>
       <c r="B17" s="4"/>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="41" t="s">
         <v>77</v>
       </c>
       <c r="D17" s="16"/>
-      <c r="F17" s="35">
+      <c r="F17" s="38">
         <f>B19</f>
         <v>0</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>78</v>
       </c>
       <c r="B18" s="4"/>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D18" s="16"/>
@@ -3714,13 +3714,13 @@
         <v>80</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="41" t="s">
         <v>81</v>
       </c>
       <c r="D19" s="16"/>
     </row>
     <row r="23" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="23" t="s">
         <v>82</v>
       </c>
       <c r="B23" s="16"/>
@@ -3785,7 +3785,7 @@
       <c r="G29" s="16"/>
     </row>
     <row r="31" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="23" t="s">
         <v>83</v>
       </c>
       <c r="B31" s="16"/>
@@ -3833,15 +3833,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A32:G35"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="A2:H2"/>
@@ -3858,6 +3849,15 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A24:G29"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.55000000000000004" bottom="0.55000000000000004" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
@@ -3995,7 +3995,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="23" t="s">
         <v>96</v>
       </c>
       <c r="B18" s="16"/>
@@ -4060,7 +4060,7 @@
       <c r="G24" s="16"/>
     </row>
     <row r="26" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="23" t="s">
         <v>97</v>
       </c>
       <c r="B26" s="16"/>
@@ -4236,7 +4236,7 @@
       <c r="F10" s="13"/>
     </row>
     <row r="31" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="23" t="s">
         <v>104</v>
       </c>
       <c r="B31" s="16"/>
@@ -4294,7 +4294,7 @@
       <c r="F37" s="16"/>
     </row>
     <row r="39" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="23" t="s">
         <v>105</v>
       </c>
       <c r="B39" s="16"/>
@@ -4416,7 +4416,7 @@
       <c r="H6" s="16"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="19" t="s">
         <v>109</v>
       </c>
       <c r="B7" s="16"/>
@@ -4427,7 +4427,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="19" t="s">
         <v>94</v>
       </c>
       <c r="B8" s="16"/>
@@ -4438,7 +4438,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="19" t="s">
         <v>110</v>
       </c>
       <c r="B9" s="16"/>
@@ -4449,7 +4449,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="19" t="s">
         <v>111</v>
       </c>
       <c r="B10" s="16"/>
@@ -4460,7 +4460,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="19" t="s">
         <v>112</v>
       </c>
       <c r="B11" s="16"/>
@@ -4471,7 +4471,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="19" t="s">
         <v>113</v>
       </c>
       <c r="B12" s="16"/>
@@ -4494,7 +4494,7 @@
       <c r="H15" s="16"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="40"/>
+      <c r="A16" s="24"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
@@ -4614,7 +4614,7 @@
       <c r="H27" s="16"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F28" s="41" t="s">
+      <c r="F28" s="25" t="s">
         <v>115</v>
       </c>
       <c r="G28" s="16"/>
@@ -4636,7 +4636,7 @@
       <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="23" t="s">
         <v>117</v>
       </c>
       <c r="B32" s="16"/>
@@ -4678,7 +4678,7 @@
       <c r="H35" s="16"/>
     </row>
     <row r="37" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="19" t="s">
+      <c r="A37" s="23" t="s">
         <v>118</v>
       </c>
       <c r="B37" s="16"/>
@@ -4720,7 +4720,7 @@
       <c r="H40" s="16"/>
     </row>
     <row r="42" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="19" t="s">
+      <c r="A42" s="23" t="s">
         <v>119</v>
       </c>
       <c r="B42" s="16"/>
@@ -4762,7 +4762,7 @@
       <c r="H45" s="16"/>
     </row>
     <row r="47" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="19" t="s">
+      <c r="A47" s="23" t="s">
         <v>120</v>
       </c>
       <c r="B47" s="16"/>
@@ -4816,7 +4816,7 @@
       <c r="H53" s="16"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="39" t="s">
+      <c r="A54" s="22" t="s">
         <v>122</v>
       </c>
       <c r="B54" s="16"/>
@@ -4849,14 +4849,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A43:H45"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A7:C7"/>
     <mergeCell ref="A48:H50"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A54:H56"/>
@@ -4873,6 +4865,14 @@
     <mergeCell ref="A33:H35"/>
     <mergeCell ref="A38:H40"/>
     <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A43:H45"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.55000000000000004" bottom="0.55000000000000004" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="portrait"/>
